--- a/inventory/swarm-technology-document-inventory.xlsx
+++ b/inventory/swarm-technology-document-inventory.xlsx
@@ -22197,7 +22197,7 @@
       </c>
       <c r="E173" s="25" t="inlineStr">
         <is>
-          <t>https://dev.epicgames.com/documentation/en-us/unreal-engine</t>
+          <t>https://dev.epicgames.com/documentation/unreal-engine/</t>
         </is>
       </c>
       <c r="F173" s="16" t="inlineStr">
@@ -22223,12 +22223,12 @@
       </c>
       <c r="K173" s="16" t="inlineStr">
         <is>
-          <t>From general knowledge, not seen this session (confirm before scraping)</t>
+          <t>Checked live on 22 September 2026 (URL corrected)</t>
         </is>
       </c>
       <c r="L173" s="16" t="inlineStr">
         <is>
-          <t>Very large; scrape only if AirSim-family work goes ahead.</t>
+          <t>Very large; scrape only if AirSim-family work goes ahead. URL corrected after live test: the en-us path redirects to a page whose links all use the locale-free /documentation/unreal-engine/ path (was https://dev.epicgames.com/documentation/en-us/unreal-engine).</t>
         </is>
       </c>
     </row>
